--- a/results/2026-10-02_quangcaominhloi_tier2.xlsx
+++ b/results/2026-10-02_quangcaominhloi_tier2.xlsx
@@ -36,18 +36,22 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="00974706"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <color rgb="000563C1"/>
       <u val="single"/>
     </font>
     <font>
+      <color rgb="00974706"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="009C6500"/>
     </font>
     <font>
-      <color rgb="00375623"/>
+      <color rgb="007F6000"/>
     </font>
     <font>
       <b val="1"/>
@@ -59,10 +63,10 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <i val="1"/>
@@ -72,14 +76,10 @@
       <color rgb="009C6500"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="12"/>
+      <color rgb="001F4E79"/>
     </font>
     <font>
-      <color rgb="007F6000"/>
-    </font>
-    <font>
-      <color rgb="001F4E79"/>
+      <color rgb="00375623"/>
     </font>
   </fonts>
   <fills count="10">
@@ -96,6 +96,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFD9B3"/>
       </patternFill>
     </fill>
@@ -106,7 +111,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -116,17 +121,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -142,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -153,57 +153,63 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -747,7 +753,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>820</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -762,54 +768,66 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>https://www.notebook.ai/documents/2802109</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Phai check tay</t>
+          <t>https://penzu.com/p/7a0fbc372732c3ec</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Link mat</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>NANG</t>
+          <t>CHET</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>bi chan captcha</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+          <t>khong thay link</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>bi robots.txt cam vao</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>BI_CHAN_CAPTCHA</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>Trang tra ve man hinh chong bot (Cloudflare / captcha).</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>Bat --js, hoac kiem tra tay. Khong tinh la mat link.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>ROBOTS_CHAN_GOOGLE</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>robots.txt cua site cam Googlebot thu thap dung duong dan nay. Trang van mo binh thuong voi nguoi, the &lt;a&gt; van con, nhung Google khong bao gio ghe vao nen link khong truyen duoc chut gia tri nao.</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Doi ben cung cap dat link o duong dan khac khong bi cam, hoac bu link moi. Bang chung: dan nguyen dong Disallow trong robots.txt cua ho.</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Thay link moi</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>bi chan</t>
+        </is>
+      </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>200</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr"/>
@@ -817,12 +835,12 @@
       <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>https://www.notebook.ai/documents/2802109</t>
+          <t>https://penzu.com/public/7a0fbc372732c3ec</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>playwright</t>
+          <t>http</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
@@ -832,24 +850,20 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>noindex (meta robots)</t>
-        </is>
-      </c>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 08:31</t>
+          <t>2026-10-02 16:30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>822</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -864,999 +878,1091 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>https://wakelet.com/wake/kP_mLLgQFPmWHPyAz_oNZ</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Link mat</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>CHET</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>thay link</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>khong ro - trang gan nhu trong</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>TRANG_NOINDEX</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>The &lt;a&gt; VAN CON tren trang, nhung trang mang the noindex nen Google khong bao gio doc toi - link khong truyen duoc chut gia tri nao.</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Coi nhu MAT LINK: mua backlink la mua gia tri truyen ve, khong phai mua mot the &lt;a&gt;. Thay bang nguon khac.</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Thay link moi</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>NOFOLLOW, TRO_SAI_TANG</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>than bai</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>cho phep</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>noreferrer noopener ugc</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>https://quangcaominhloi.vn/treo-bang-ron-co-phuon-toan-quoc</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>treo băng rôn</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>https://wakelet.com/wake/kP_mLLgQFPmWHPyAz_oNZ</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>FOUND</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>noindex (meta robots)</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Web 2.0</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>https://share.evernote.com/note/0ebfc4e2-9ced-f600-fa23-044aa1b06d5e</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Phai check tay</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>NANG</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>trang trong</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>khong ro - trang gan nhu trong</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>TRANG_RONG</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Trang tai duoc nhung gan nhu khong co noi dung.</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>Kiem tra tay - co the bai bi go noi dung nhung URL van song.</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>cho phep</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr"/>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>https://lite.evernote.com/note/0ebfc4e2-9ced-f600-fa23-044aa1b06d5e</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="Z4" s="5" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="AA4" s="5" t="inlineStr"/>
+      <c r="AB4" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Web 2.0</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/view/treobangroncophuon/</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Link con</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>CANH BAO</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>thay link</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>thay link</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>TRO_SAI_TANG</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>Link VAN CON va van tro ve he thong cua minh, nhung roi vao tang khac voi khai bao trong config. Xem cot khop_tang de biet no tro vao dau.</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>Khong phai link hong - khong dua vao yeu cau bu. Hoac sua lai khai bao tier trong config cho dung thuc te, hoac dat lai link cho dung tang.</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>Sua link</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr"/>
+      <c r="N5" s="9" t="inlineStr"/>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>footer</t>
+        </is>
+      </c>
+      <c r="P5" s="9" t="inlineStr">
+        <is>
+          <t>cho phep</t>
+        </is>
+      </c>
+      <c r="Q5" s="9" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R5" s="9" t="inlineStr">
+        <is>
+          <t>dofollow</t>
+        </is>
+      </c>
+      <c r="S5" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T5" s="9" t="inlineStr">
+        <is>
+          <t>https://quangcaominhloi.vn/treo-bang-ron-co-phuon-toan-quoc</t>
+        </is>
+      </c>
+      <c r="U5" s="9" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="V5" s="9" t="inlineStr">
+        <is>
+          <t>treo băng rôn</t>
+        </is>
+      </c>
+      <c r="W5" s="9" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/view/treobangroncophuon/</t>
+        </is>
+      </c>
+      <c r="X5" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="Y5" s="9" t="inlineStr">
+        <is>
+          <t>FOUND</t>
+        </is>
+      </c>
+      <c r="Z5" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="AA5" s="9" t="inlineStr"/>
+      <c r="AB5" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Web 2.0</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>https://hoamai90.blogspot.com/2026/09/treo-bang-ron-va-treo-co-phuon.html</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Link con</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>CANH BAO</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>thay link</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>thay link (canonical khac)</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>TRO_SAI_TANG</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>Link VAN CON va van tro ve he thong cua minh, nhung roi vao tang khac voi khai bao trong config. Xem cot khop_tang de biet no tro vao dau.</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>Khong phai link hong - khong dua vao yeu cau bu. Hoac sua lai khai bao tier trong config cho dung thuc te, hoac dat lai link cho dung tang.</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>Sua link</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>CANONICAL_CO_LINK</t>
+        </is>
+      </c>
+      <c r="N6" s="9" t="inlineStr"/>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t>than bai</t>
+        </is>
+      </c>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
+          <t>cho phep</t>
+        </is>
+      </c>
+      <c r="Q6" s="9" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R6" s="9" t="inlineStr">
+        <is>
+          <t>dofollow</t>
+        </is>
+      </c>
+      <c r="S6" s="9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T6" s="9" t="inlineStr">
+        <is>
+          <t>https://quangcaominhloi.vn/treo-bang-ron-co-phuon-toan-quoc</t>
+        </is>
+      </c>
+      <c r="U6" s="9" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="V6" s="9" t="inlineStr">
+        <is>
+          <t>treo băng rôn</t>
+        </is>
+      </c>
+      <c r="W6" s="9" t="inlineStr">
+        <is>
+          <t>https://hoamai90.blogspot.com/2026/09/treo-bang-ron-va-treo-co-phuon.html</t>
+        </is>
+      </c>
+      <c r="X6" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="Y6" s="9" t="inlineStr">
+        <is>
+          <t>FOUND</t>
+        </is>
+      </c>
+      <c r="Z6" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AA6" s="9" t="inlineStr">
+        <is>
+          <t>canonical khac</t>
+        </is>
+      </c>
+      <c r="AB6" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Web 2.0</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>https://www.notebook.ai/documents/2802109</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Phai check tay</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>CANH BAO</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>bi chan captcha</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>khong ro - bi chan HTTP 403</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>BI_CHAN_CAPTCHA</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>Trang tra ve man hinh chong bot (Cloudflare / captcha).</t>
+        </is>
+      </c>
+      <c r="K7" s="12" t="inlineStr">
+        <is>
+          <t>Bat --js, hoac kiem tra tay. Khong tinh la mat link.</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr"/>
+      <c r="M7" s="9" t="inlineStr"/>
+      <c r="N7" s="9" t="inlineStr"/>
+      <c r="O7" s="9" t="inlineStr"/>
+      <c r="P7" s="9" t="inlineStr">
+        <is>
+          <t>khong ro</t>
+        </is>
+      </c>
+      <c r="Q7" s="9" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="R7" s="9" t="inlineStr"/>
+      <c r="S7" s="9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T7" s="9" t="inlineStr"/>
+      <c r="U7" s="9" t="inlineStr"/>
+      <c r="V7" s="9" t="inlineStr"/>
+      <c r="W7" s="9" t="inlineStr">
+        <is>
+          <t>https://www.notebook.ai/documents/2802109</t>
+        </is>
+      </c>
+      <c r="X7" s="9" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="Y7" s="9" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="Z7" s="9" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="AA7" s="9" t="inlineStr">
+        <is>
+          <t>noindex (meta robots)</t>
+        </is>
+      </c>
+      <c r="AB7" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Web 2.0</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
           <t>https://olive-turquoise-6c4.notion.site/Treo-b-ng-r-n-v-treo-c-ph-n-3e40fe9911f780328487dd4d7a04bf8b</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Phai check tay</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>NANG</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>CANH BAO</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>chua doc duoc noi dung</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>khong ro - bi chan HTTP 403</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>CHUA_RENDER_DUOC</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>Da mo bang Chromium nhung van khong tai duoc noi dung that (trang treo, chan bot tan goc, hoac qua cham).</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K8" s="12" t="inlineStr">
         <is>
           <t>Mo tay bang trinh duyet. KHONG tinh la mat link.</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr"/>
+      <c r="M8" s="9" t="inlineStr"/>
+      <c r="N8" s="9" t="inlineStr"/>
+      <c r="O8" s="9" t="inlineStr"/>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>cho phep</t>
+        </is>
+      </c>
+      <c r="Q8" s="9" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="R8" s="9" t="inlineStr"/>
+      <c r="S8" s="9" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr"/>
-      <c r="U3" s="2" t="inlineStr"/>
-      <c r="V3" s="2" t="inlineStr"/>
-      <c r="W3" s="2" t="inlineStr">
+      <c r="T8" s="9" t="inlineStr"/>
+      <c r="U8" s="9" t="inlineStr"/>
+      <c r="V8" s="9" t="inlineStr"/>
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>https://olive-turquoise-6c4.notion.site/Treo-b-ng-r-n-v-treo-c-ph-n-3e40fe9911f780328487dd4d7a04bf8b</t>
         </is>
       </c>
-      <c r="X3" s="2" t="inlineStr">
+      <c r="X8" s="9" t="inlineStr">
         <is>
           <t>http</t>
         </is>
       </c>
-      <c r="Y3" s="2" t="inlineStr">
+      <c r="Y8" s="9" t="inlineStr">
         <is>
           <t>NOT_FOUND</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>3.9</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr">
+      <c r="Z8" s="9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AA8" s="9" t="inlineStr">
         <is>
           <t>js:TimeoutError</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02 08:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>876</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="AB8" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Web 2.0</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>https://ofuse.me/e/410823</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Phai check tay</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>NANG</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>CANH BAO</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>bi chan captcha</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>khong ro - bi chan HTTP 403</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>BI_CHAN_CAPTCHA</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J9" s="12" t="inlineStr">
         <is>
           <t>Trang tra ve man hinh chong bot (Cloudflare / captcha).</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K9" s="12" t="inlineStr">
         <is>
           <t>Bat --js, hoac kiem tra tay. Khong tinh la mat link.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr"/>
+      <c r="M9" s="9" t="inlineStr"/>
+      <c r="N9" s="9" t="inlineStr"/>
+      <c r="O9" s="9" t="inlineStr"/>
+      <c r="P9" s="9" t="inlineStr">
+        <is>
+          <t>khong ro</t>
+        </is>
+      </c>
+      <c r="Q9" s="9" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="R9" s="9" t="inlineStr"/>
+      <c r="S9" s="9" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr"/>
-      <c r="U4" s="2" t="inlineStr"/>
-      <c r="V4" s="2" t="inlineStr"/>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="T9" s="9" t="inlineStr"/>
+      <c r="U9" s="9" t="inlineStr"/>
+      <c r="V9" s="9" t="inlineStr"/>
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>https://ofuse.me/e/410823</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
+      <c r="X9" s="9" t="inlineStr">
         <is>
           <t>playwright</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="Y9" s="9" t="inlineStr">
         <is>
           <t>NOT_FOUND</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>HTTP 429</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02 08:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>878</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="Z9" s="9" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="AA9" s="9" t="inlineStr">
+        <is>
+          <t>HTTP 403</t>
+        </is>
+      </c>
+      <c r="AB9" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Web 2.0</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>https://share.evernote.com/note/0ebfc4e2-9ced-f600-fa23-044aa1b06d5e</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Phai check tay</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>NANG</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>trang trong</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>TRANG_RONG</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>Trang tai duoc nhung gan nhu khong co noi dung.</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>Kiem tra tay - co the bai bi go noi dung nhung URL van song.</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>https://www.pearltrees.com/minhloitc/item825311633</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Link con</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>CANH BAO</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>thay link</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>thay link</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>TRO_SAI_TANG</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>Link VAN CON va van tro ve he thong cua minh, nhung roi vao tang khac voi khai bao trong config. Xem cot khop_tang de biet no tro vao dau.</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>Khong phai link hong - khong dua vao yeu cau bu. Hoac sua lai khai bao tier trong config cho dung thuc te, hoac dat lai link cho dung tang.</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>Sua link</t>
+        </is>
+      </c>
+      <c r="M10" s="9" t="inlineStr"/>
+      <c r="N10" s="9" t="inlineStr"/>
+      <c r="O10" s="9" t="inlineStr">
+        <is>
+          <t>than bai</t>
+        </is>
+      </c>
+      <c r="P10" s="9" t="inlineStr">
+        <is>
+          <t>cho phep</t>
+        </is>
+      </c>
+      <c r="Q10" s="9" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="R10" s="9" t="inlineStr">
+        <is>
+          <t>dofollow</t>
+        </is>
+      </c>
+      <c r="S10" s="9" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr"/>
-      <c r="U5" s="2" t="inlineStr"/>
-      <c r="V5" s="2" t="inlineStr"/>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>https://lite.evernote.com/note/0ebfc4e2-9ced-f600-fa23-044aa1b06d5e</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>playwright</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02 08:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>870</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="T10" s="9" t="inlineStr">
+        <is>
+          <t>https://quangcaominhloi.vn/treo-bang-ron-co-phuon-toan-quoc</t>
+        </is>
+      </c>
+      <c r="U10" s="9" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="V10" s="9" t="inlineStr">
+        <is>
+          <t>treo băng rôn</t>
+        </is>
+      </c>
+      <c r="W10" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pearltrees.com/minhloitc/item825311633</t>
+        </is>
+      </c>
+      <c r="X10" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="Y10" s="9" t="inlineStr">
+        <is>
+          <t>FOUND</t>
+        </is>
+      </c>
+      <c r="Z10" s="9" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="AA10" s="9" t="inlineStr"/>
+      <c r="AB10" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Web 2.0</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>https://penzu.com/p/7a0fbc372732c3ec</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>https://magicly.bio/minhloitc/Treo-bang-ron-va-treo-co-phuon</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Link con</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>TOT</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>CANH BAO</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>thay link</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>Link song, tro dung URL dich (che do loose: khong xet nofollow / noindex).</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>Khong can lam gi.</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr"/>
-      <c r="N6" s="6" t="inlineStr"/>
-      <c r="O6" s="6" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>thay link (nofollow)</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>TRO_SAI_TANG</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>Link VAN CON va van tro ve he thong cua minh, nhung roi vao tang khac voi khai bao trong config. Xem cot khop_tang de biet no tro vao dau.</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
+        <is>
+          <t>Khong phai link hong - khong dua vao yeu cau bu. Hoac sua lai khai bao tier trong config cho dung thuc te, hoac dat lai link cho dung tang.</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>Sua link</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>NOFOLLOW</t>
+        </is>
+      </c>
+      <c r="N11" s="9" t="inlineStr"/>
+      <c r="O11" s="9" t="inlineStr">
         <is>
           <t>than bai</t>
         </is>
       </c>
-      <c r="P6" s="6" t="inlineStr"/>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="P11" s="9" t="inlineStr">
+        <is>
+          <t>cho phep</t>
+        </is>
+      </c>
+      <c r="Q11" s="9" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>dofollow</t>
-        </is>
-      </c>
-      <c r="S6" s="6" t="inlineStr">
+      <c r="R11" s="9" t="inlineStr">
+        <is>
+          <t>nofollow noreferrer noopener</t>
+        </is>
+      </c>
+      <c r="S11" s="9" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="T6" s="6" t="inlineStr">
+      <c r="T11" s="9" t="inlineStr">
         <is>
           <t>https://quangcaominhloi.vn/treo-bang-ron-co-phuon-toan-quoc</t>
         </is>
       </c>
-      <c r="U6" s="6" t="inlineStr">
+      <c r="U11" s="9" t="inlineStr">
         <is>
           <t>money</t>
         </is>
       </c>
-      <c r="V6" s="6" t="inlineStr">
+      <c r="V11" s="9" t="inlineStr">
         <is>
           <t>treo băng rôn</t>
         </is>
       </c>
-      <c r="W6" s="6" t="inlineStr">
-        <is>
-          <t>https://penzu.com/public/7a0fbc372732c3ec</t>
-        </is>
-      </c>
-      <c r="X6" s="6" t="inlineStr">
-        <is>
-          <t>playwright</t>
-        </is>
-      </c>
-      <c r="Y6" s="6" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
+        <is>
+          <t>https://magicly.bio/minhloitc/Treo-bang-ron-va-treo-co-phuon</t>
+        </is>
+      </c>
+      <c r="X11" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="Y11" s="9" t="inlineStr">
         <is>
           <t>FOUND</t>
         </is>
       </c>
-      <c r="Z6" s="6" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="AA6" s="6" t="inlineStr"/>
-      <c r="AB6" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-02 08:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>871</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Web 2.0</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>https://sites.google.com/view/treobangroncophuon/</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Link con</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>TOT</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>thay link</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>Link song, tro dung URL dich (che do loose: khong xet nofollow / noindex).</t>
-        </is>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>Khong can lam gi.</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr"/>
-      <c r="M7" s="6" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr"/>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>footer</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr"/>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>dofollow</t>
-        </is>
-      </c>
-      <c r="S7" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="T7" s="6" t="inlineStr">
-        <is>
-          <t>https://quangcaominhloi.vn/treo-bang-ron-co-phuon-toan-quoc</t>
-        </is>
-      </c>
-      <c r="U7" s="6" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="V7" s="6" t="inlineStr">
-        <is>
-          <t>treo băng rôn</t>
-        </is>
-      </c>
-      <c r="W7" s="6" t="inlineStr">
-        <is>
-          <t>https://sites.google.com/view/treobangroncophuon/</t>
-        </is>
-      </c>
-      <c r="X7" s="6" t="inlineStr">
-        <is>
-          <t>http</t>
-        </is>
-      </c>
-      <c r="Y7" s="6" t="inlineStr">
-        <is>
-          <t>FOUND</t>
-        </is>
-      </c>
-      <c r="Z7" s="6" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="AA7" s="6" t="inlineStr"/>
-      <c r="AB7" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-02 08:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>872</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Web 2.0</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>https://wakelet.com/wake/kP_mLLgQFPmWHPyAz_oNZ</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Link con</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>TOT</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>thay link</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>Link song, tro dung URL dich (che do loose: khong xet nofollow / noindex).</t>
-        </is>
-      </c>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>Khong can lam gi.</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr"/>
-      <c r="M8" s="6" t="inlineStr"/>
-      <c r="N8" s="6" t="inlineStr"/>
-      <c r="O8" s="6" t="inlineStr">
-        <is>
-          <t>than bai</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="inlineStr"/>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>noreferrer noopener ugc</t>
-        </is>
-      </c>
-      <c r="S8" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="T8" s="6" t="inlineStr">
-        <is>
-          <t>https://quangcaominhloi.vn/treo-bang-ron-co-phuon-toan-quoc</t>
-        </is>
-      </c>
-      <c r="U8" s="6" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="V8" s="6" t="inlineStr">
-        <is>
-          <t>treo băng rôn</t>
-        </is>
-      </c>
-      <c r="W8" s="6" t="inlineStr">
-        <is>
-          <t>https://wakelet.com/wake/kP_mLLgQFPmWHPyAz_oNZ</t>
-        </is>
-      </c>
-      <c r="X8" s="6" t="inlineStr">
-        <is>
-          <t>playwright</t>
-        </is>
-      </c>
-      <c r="Y8" s="6" t="inlineStr">
-        <is>
-          <t>FOUND</t>
-        </is>
-      </c>
-      <c r="Z8" s="6" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
-      <c r="AA8" s="6" t="inlineStr">
-        <is>
-          <t>noindex (meta robots)</t>
-        </is>
-      </c>
-      <c r="AB8" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-02 08:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>873</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Web 2.0</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>https://hoamai90.blogspot.com/2026/09/treo-bang-ron-va-treo-co-phuon.html</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Link con</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>TOT</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>thay link</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>Link song, tro dung URL dich (che do loose: khong xet nofollow / noindex).</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>Khong can lam gi.</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr"/>
-      <c r="M9" s="6" t="inlineStr"/>
-      <c r="N9" s="6" t="inlineStr"/>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>than bai</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr"/>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>dofollow</t>
-        </is>
-      </c>
-      <c r="S9" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="T9" s="6" t="inlineStr">
-        <is>
-          <t>https://quangcaominhloi.vn/treo-bang-ron-co-phuon-toan-quoc</t>
-        </is>
-      </c>
-      <c r="U9" s="6" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="V9" s="6" t="inlineStr">
-        <is>
-          <t>treo băng rôn</t>
-        </is>
-      </c>
-      <c r="W9" s="6" t="inlineStr">
-        <is>
-          <t>https://hoamai90.blogspot.com/2026/09/treo-bang-ron-va-treo-co-phuon.html</t>
-        </is>
-      </c>
-      <c r="X9" s="6" t="inlineStr">
-        <is>
-          <t>http</t>
-        </is>
-      </c>
-      <c r="Y9" s="6" t="inlineStr">
-        <is>
-          <t>FOUND</t>
-        </is>
-      </c>
-      <c r="Z9" s="6" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="AA9" s="6" t="inlineStr"/>
-      <c r="AB9" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-02 08:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>877</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Web 2.0</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.pearltrees.com/minhloitc/item825311633</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Link con</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>TOT</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>thay link</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr"/>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>Link song, tro dung URL dich (che do loose: khong xet nofollow / noindex).</t>
-        </is>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>Khong can lam gi.</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr"/>
-      <c r="M10" s="6" t="inlineStr"/>
-      <c r="N10" s="6" t="inlineStr"/>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>than bai</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr"/>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>dofollow</t>
-        </is>
-      </c>
-      <c r="S10" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="T10" s="6" t="inlineStr">
-        <is>
-          <t>https://quangcaominhloi.vn/treo-bang-ron-co-phuon-toan-quoc</t>
-        </is>
-      </c>
-      <c r="U10" s="6" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="V10" s="6" t="inlineStr">
-        <is>
-          <t>treo băng rôn</t>
-        </is>
-      </c>
-      <c r="W10" s="6" t="inlineStr">
-        <is>
-          <t>https://www.pearltrees.com/minhloitc/item825311633</t>
-        </is>
-      </c>
-      <c r="X10" s="6" t="inlineStr">
-        <is>
-          <t>http</t>
-        </is>
-      </c>
-      <c r="Y10" s="6" t="inlineStr">
-        <is>
-          <t>FOUND</t>
-        </is>
-      </c>
-      <c r="Z10" s="6" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="AA10" s="6" t="inlineStr"/>
-      <c r="AB10" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-02 08:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>879</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Web 2.0</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>https://magicly.bio/minhloitc/Treo-bang-ron-va-treo-co-phuon</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>Link con</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>TOT</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>thay link</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr"/>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>Link song, tro dung URL dich (che do loose: khong xet nofollow / noindex).</t>
-        </is>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>Khong can lam gi.</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr"/>
-      <c r="M11" s="6" t="inlineStr"/>
-      <c r="N11" s="6" t="inlineStr"/>
-      <c r="O11" s="6" t="inlineStr">
-        <is>
-          <t>than bai</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="inlineStr"/>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>nofollow noreferrer noopener</t>
-        </is>
-      </c>
-      <c r="S11" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="T11" s="6" t="inlineStr">
-        <is>
-          <t>https://quangcaominhloi.vn/treo-bang-ron-co-phuon-toan-quoc</t>
-        </is>
-      </c>
-      <c r="U11" s="6" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="V11" s="6" t="inlineStr">
-        <is>
-          <t>treo băng rôn</t>
-        </is>
-      </c>
-      <c r="W11" s="6" t="inlineStr">
-        <is>
-          <t>https://magicly.bio/minhloitc/Treo-bang-ron-va-treo-co-phuon</t>
-        </is>
-      </c>
-      <c r="X11" s="6" t="inlineStr">
-        <is>
-          <t>http</t>
-        </is>
-      </c>
-      <c r="Y11" s="6" t="inlineStr">
-        <is>
-          <t>FOUND</t>
-        </is>
-      </c>
-      <c r="Z11" s="6" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AA11" s="6" t="inlineStr"/>
-      <c r="AB11" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-02 08:31</t>
+      <c r="Z11" s="9" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AA11" s="9" t="inlineStr"/>
+      <c r="AB11" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:30</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1918,344 +2024,527 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Che do check</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>loose - chi can vao duoc trang va thay link ve dich</t>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>CHOT LAI - doc dong nay truoc</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>CHOT LAI - doc dong nay truoc</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Ket luan</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>So link</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Ty le</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Nghia la gi</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Phai lam gi</t>
         </is>
       </c>
     </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Link con</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Tool doc duoc trang va nhin thay the &lt;a&gt; tro ve money site.</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>KHONG can mo tay. Trong so nay co 0 link hoan hao (muc TOT).</t>
+        </is>
+      </c>
+    </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Link con</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Tool doc duoc trang va nhin thay the &lt;a&gt; tro ve money site.</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>KHONG can mo tay. Trong so nay co 6 link hoan hao (muc TOT).</t>
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Link mat</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Tool doc duoc trang va chac chan link khong con gia tri (404/410/bai bi go/trang noindex), hoac Googlebot khong thay link du nguoi xem van thay.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>KHONG can mo tay. Thay bang nguon moi.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>Link mat</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>Tool doc duoc trang va chac chan link khong con gia tri (404/410/bai bi go/trang noindex), hoac Googlebot khong thay link du nguoi xem van thay.</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>KHONG can mo tay. Thay bang nguon moi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Phai check tay</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B8" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>40.0%</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Tool KHONG doc duoc noi dung that (chan bot, captcha, dang nhap, chua render JS...). Day CHUA phai ket luan mat link.</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>PHAI xu ly: 0 link chi can chay lai tool, 4 link phai mo trinh duyet. Danh sach o sheet 'Can check tay'.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>TONG</t>
         </is>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B9" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>NGUOI XEM va GOOGLE - tool ket luan theo nhung gi Google thay</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>THEO TIER</t>
-        </is>
-      </c>
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Tinh trang</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>So link</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr"/>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Nghia la gi</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>Tong</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Link con</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>Link mat</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>Phai check tay</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>CHET</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>NANG</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Google thay link binh thuong</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>Googlebot tai duoc trang va doc thay the &lt;a&gt;. Ket luan dua tren chinh trang nay.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Google bi bao 404 - nguoi xem van thay</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>Trang tra 404 rieng cho Googlebot. Tinh la Link mat, doi bu.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Link bi giau voi Google</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>0</v>
       </c>
-      <c r="G14" t="n">
-        <v>4</v>
-      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>Nguoi xem thay link, trang gui cho Googlebot thi khong co. Tinh la Link mat, doi bu.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>THEO MA LOI - sap theo muc do nghiem trong</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cloaking - Google thay, nguoi dung bi chuyen di</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>Google van thay link nen van la Link con. Chi ghi chu: site dung cloaking co rui ro bi phat.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Ma loi</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Muc do</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>So luong</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Chan doan</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Viec can lam</t>
-        </is>
-      </c>
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>robots.txt cam Google</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Google khong duoc phep vao. Tinh la Link mat.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>BI_CHAN_CAPTCHA</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>NANG</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>Trang tra ve man hinh chong bot (Cloudflare / captcha).</t>
-        </is>
-      </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>Bat --js, hoac kiem tra tay. Khong tinh la mat link.</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Google tra loi khong ro</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>Googlebot bi chan 403/429, trang trong, hoac link chen bang JS. Nhieu site chi chan Googlebot gia, nen tool giu ket luan theo nguoi xem.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>CHUA_RENDER_DUOC</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>NANG</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>Da mo bang Chromium nhung van khong tai duoc noi dung that (trang treo, chan bot tan goc, hoac qua cham).</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>Mo tay bang trinh duyet. KHONG tinh la mat link.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>TRANG_RONG</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>NANG</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>Trang tai duoc nhung gan nhu khong co noi dung.</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>Kiem tra tay - co the bai bi go noi dung nhung URL van song.</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chua hoi Googlebot</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>Trang khong phan hoi (DNS, timeout, tu choi ket noi) - doi User-Agent khong doi duoc gi.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>TOT</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>Link song, dofollow, tro dung URL dich.</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="inlineStr">
-        <is>
-          <t>Khong can lam gi.</t>
+          <t>THEO TIER</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Tong</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Link con</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Link mat</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>Phai check tay</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>CHET</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>NANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>THEO MA LOI - sap theo muc do nghiem trong</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Ma loi</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Muc do</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>So luong</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Chan doan</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Viec can lam</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>ROBOTS_CHAN_GOOGLE</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>CHET</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>robots.txt cua site cam Googlebot thu thap dung duong dan nay. Trang van mo binh thuong voi nguoi, the &lt;a&gt; van con, nhung Google khong bao gio ghe vao nen link khong truyen duoc chut gia tri nao.</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>Doi ben cung cap dat link o duong dan khac khong bi cam, hoac bu link moi. Bang chung: dan nguyen dong Disallow trong robots.txt cua ho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>TRANG_NOINDEX</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>CHET</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>The &lt;a&gt; VAN CON tren trang, nhung trang mang the noindex nen Google khong bao gio doc toi - link khong truyen duoc chut gia tri nao.</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>Coi nhu MAT LINK: mua backlink la mua gia tri truyen ve, khong phai mua mot the &lt;a&gt;. Thay bang nguon khac.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>TRANG_RONG</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>NANG</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>Trang tai duoc nhung gan nhu khong co noi dung.</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>Kiem tra tay - co the bai bi go noi dung nhung URL van song.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>TRO_SAI_TANG</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>CANH BAO</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>Link VAN CON va van tro ve he thong cua minh, nhung roi vao tang khac voi khai bao trong config. Xem cot khop_tang de biet no tro vao dau.</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>Khong phai link hong - khong dua vao yeu cau bu. Hoac sua lai khai bao tier trong config cho dung thuc te, hoac dat lai link cho dung tang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>BI_CHAN_CAPTCHA</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>CANH BAO</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>Trang tra ve man hinh chong bot (Cloudflare / captcha).</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>Bat --js, hoac kiem tra tay. Khong tinh la mat link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>CHUA_RENDER_DUOC</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>CANH BAO</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>Da mo bang Chromium nhung van khong tai duoc noi dung that (trang treo, chan bot tan goc, hoac qua cham).</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>Mo tay bang trinh duyet. KHONG tinh la mat link.</t>
         </is>
       </c>
     </row>
@@ -2283,14 +2572,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>DANH SACH LINK TOOL CHUA KET LUAN DUOC</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>Nhung link duoi day KHONG phai la link mat. Tool bi chan hoac chua doc duoc noi dung that nen khong dam ket luan.</t>
         </is>
@@ -2343,148 +2632,148 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Mo trinh duyet</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Web 2.0</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>https://www.notebook.ai/documents/2802109</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>BI_CHAN_CAPTCHA</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>Trang tra ve man hinh chong bot (Cloudflare / captcha).</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t>Mo URL bang trinh duyet, qua captcha roi Ctrl+F tim link</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Mo trinh duyet</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>Web 2.0</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>https://ofuse.me/e/410823</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>BI_CHAN_CAPTCHA</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>Trang tra ve man hinh chong bot (Cloudflare / captcha).</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>Mo URL bang trinh duyet, qua captcha roi Ctrl+F tim link</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Mo trinh duyet</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>Web 2.0</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>https://olive-turquoise-6c4.notion.site/Treo-b-ng-r-n-v-treo-c-ph-n-3e40fe9911f780328487dd4d7a04bf8b</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>CHUA_RENDER_DUOC</t>
         </is>
       </c>
-      <c r="F7" s="24" t="inlineStr">
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>Da mo bang Chromium nhung van khong tai duoc noi dung that (trang treo, chan bot tan goc, hoac qua cham).</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G7" s="28" t="inlineStr">
         <is>
           <t>Da mo bang Chromium ma van khong tai duoc. Mo tay bang trinh duyet, doi trang nap xong roi Ctrl+F tim money site</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Mo trinh duyet</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Web 2.0</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>https://share.evernote.com/note/0ebfc4e2-9ced-f600-fa23-044aa1b06d5e</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>TRANG_RONG</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>Trang tai duoc nhung gan nhu khong co noi dung.</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G8" s="28" t="inlineStr">
         <is>
           <t>Mo URL xem bai con noi dung khong hay chi con vo trang</t>
         </is>
@@ -2508,7 +2797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2517,250 +2806,315 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>KET LUAN - co phai mo tay kiem tra khong?</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Ket luan</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Mau</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>Y nghia</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Link con</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr"/>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>Tool vao duoc trang va nhin thay the &lt;a&gt; tro ve dich. Chac chan con link. Khong can mo tay. Gom ca link tro sai tang, nofollow, noindex, robots.txt chan (che do 'mode: loose' bo qua cac thu do; xem cot rel / indexable neu can).</t>
+      <c r="B3" s="15" t="inlineStr"/>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Tool nhin thay the &lt;a&gt; va trang co the duoc index. Chac chan con link. Khong can mo tay. Gom ca link tro sai tang va link nofollow (Google khong truyen suc manh nhung van co traffic).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Link mat</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr"/>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>Tool vao duoc trang va chac chan khong con link: 404, 410, domain het han, bai bi go, trang khong con the &lt;a&gt; ve dich. Khong can mo tay.</t>
+      <c r="B4" s="17" t="inlineStr"/>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Tool doc duoc trang va chac chan link khong con gia tri: 404, 410, bai bi go, hoac trang mang the noindex (Google khong doc toi nen the &lt;a&gt; vo nghia). Khong can mo tay.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>Phai check tay</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr"/>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr"/>
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>Tool chua doc duoc noi dung that. CHUA ket luan. Xem sheet 'Can check tay'.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>MUC DO - neu phai xu ly thi gap den dau?</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Muc do</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Mau</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>Y nghia</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>CHET</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr"/>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr"/>
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>Link mat han. Phai thay bang nguon moi.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>NANG</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr"/>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr"/>
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>Link con nhung dang hong. Xu ly som.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>CANH BAO</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr"/>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr"/>
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>Link con, gia tri thap hon ky vong hoac chua ket luan duoc.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>GHI CHU</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr"/>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr"/>
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Khong sai, chi ghi chu de biet.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>TOT</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr"/>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr"/>
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>Tot, khong can lam gi.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
-        <is>
-          <t>CHE DO LONG - chi can vao duoc trang va thay link ve dich</t>
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>HAI GOC NHIN - vi sao mo link ra van thay ma tool bao mat?</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>Nguyen tac</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" s="28" t="inlineStr">
-        <is>
-          <t>Config dang dat 'mode: loose': vao duoc trang va thay the &lt;a&gt; tro ve dich la Link con. Khong xet nofollow / noindex / canonical / robots.txt / Googlebot. Doi 'mode: strict' de check theo Google.</t>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Tool ket luan theo NHUNG GI GOOGLEBOT THAY, khong theo nhung gi nguoi mo trang thay. Google chi truyen gia tri qua trang ma no doc duoc.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>Nguoi xem thay</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" s="28" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>Mo URL bang trinh duyet thuong (User-Agent Chrome).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>Google thay</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Tai lai dung URL do voi User-Agent Googlebot. Hai cot to do dam la cho hai ben thay khac nhau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>Google bi bao 404</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>Nguoi xem thay link, Googlebot nhan 404 -&gt; Link mat. Kiem chung: search.google.com/test/rich-results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>Giau link voi Google</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>Nguoi xem thay link, trang gui cho Googlebot khong co link -&gt; Link mat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>Cloaking</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>Googlebot thay link, nguoi dung bi chuyen di hoac bao loi -&gt; van Link con, chi ghi chu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>Khong ro</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>Googlebot bi 403/429/captcha: nhieu site chi chan Googlebot GIA (khong phai IP cua Google), nen tool KHONG ket luan tu do va giu ket qua cua nguoi xem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Yeu cau</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" s="28" t="inlineStr">
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>'Thay link moi' = phai dang bai khac. 'Sua link' = ben cung cap sua ngay tren bai cu (doi dofollow, doi dich, mo cong khai). 'Sua tang tren' = loi nam o URL tang tren.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Dich tang tren</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" s="28" t="inlineStr">
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>URL tang tren ma link nay tro vao con song khong. 'DA CHET' nghia la link nay van nguyen nhung gia tri dung lai o do.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Vi tri link</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" s="28" t="inlineStr">
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>Link nam o dau tren trang: than bai / binh luan / ho so / sidebar / footer / menu. Link o footer, sidebar gia tri thap hon link trong than bai.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Luu y</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
         <is>
           <t>Muc do da duoc dieu chinh theo 'priority' cua tung tier trong file config: tier uu tien 1 bi nang muc, tier uu tien tu 4 tro len duoc ha muc.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Luu y</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
         <is>
           <t>Cot 'Khop tang' cho biet link thuc su roi vao tang nao (money / tier 2 / tier 3...). Lech so voi dich dau tien khai trong 'targets' cua tier thi mang ma TRO_SAI_TANG - link van con, chi la so do tang tren giay khong khop thuc te.</t>
         </is>
